--- a/港岛-半山-雅盈峰/雅盈峰_销控明细表.xlsx
+++ b/港岛-半山-雅盈峰/雅盈峰_销控明细表.xlsx
@@ -1183,7 +1183,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7538,7 +7538,7 @@
           <t>A | 1608呎 (4+房)
 $10323万
 $64,200/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -7546,7 +7546,7 @@
           <t>B | 1254呎 (3房)
 $7499万
 $59,800/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr"/>
@@ -7592,7 +7592,7 @@
           <t>A | 1608呎 (4+房)
 $9710万
 $60,388/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -7600,7 +7600,7 @@
           <t>B | 1254呎 (3房)
 $9029万
 $72,000/呎
-(26年-07月-03日)</t>
+(26年-07月-04日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr"/>
@@ -7619,7 +7619,7 @@
           <t>A | 1608呎 (4+房)
 $10934万
 $68,000/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -7627,7 +7627,7 @@
           <t>B | 1254呎 (3房)
 $7773万
 $61,987/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr"/>
@@ -7646,7 +7646,7 @@
           <t>A | 1029呎 (3房)
 $5043万
 $49,009/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -7654,7 +7654,7 @@
           <t>B | 1074呎 (3房)
 $5934万
 $55,255/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -7662,7 +7662,7 @@
           <t>C | 1017呎 (3房)
 $4423万
 $43,486/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr"/>
@@ -7680,7 +7680,7 @@
           <t>A | 1029呎 (3房)
 $5094万
 $49,500/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -7688,7 +7688,7 @@
           <t>B | 1074呎 (3房)
 $6874万
 $64,000/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -7696,7 +7696,7 @@
           <t>C | 1017呎 (3房)
 $4882万
 $48,000/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr"/>
@@ -7714,7 +7714,7 @@
           <t>A | 1029呎 (3房)
 $4939万
 $48,000/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -7722,7 +7722,7 @@
           <t>B | 1074呎 (3房)
 $6307万
 $58,724/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -7730,7 +7730,7 @@
           <t>C | 1017呎 (3房)
 $5270万
 $51,816/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr"/>
@@ -7748,7 +7748,7 @@
           <t>A | 1029呎 (3房)
 $4507万
 $43,800/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -7756,7 +7756,7 @@
           <t>B | 1074呎 (3房)
 $5083万
 $47,326/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -7764,7 +7764,7 @@
           <t>C | 1017呎 (3房)
 $4363万
 $42,900/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr"/>
@@ -7782,7 +7782,7 @@
           <t>A | 1029呎 (3房)
 $4409万
 $42,845/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -7790,7 +7790,7 @@
           <t>B | 1074呎 (3房)
 $5058万
 $47,095/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -7798,7 +7798,7 @@
           <t>C | 1017呎 (3房)
 $4924万
 $48,416/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr"/>
@@ -7816,7 +7816,7 @@
           <t>A | 1029呎 (3房)
 $4394万
 $42,700/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -7824,7 +7824,7 @@
           <t>B | 1074呎 (3房)
 $5102万
 $47,500/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -7832,7 +7832,7 @@
           <t>C | 1017呎 (3房)
 $4832万
 $47,516/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr"/>
@@ -7850,7 +7850,7 @@
           <t>A | 1029呎 (3房)
 $4322万
 $42,000/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7858,7 +7858,7 @@
           <t>B | 1074呎 (3房)
 $5134万
 $47,800/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7866,7 +7866,7 @@
           <t>C | 1017呎 (3房)
 $4383万
 $43,100/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr"/>
@@ -7884,7 +7884,7 @@
           <t>A | 1029呎 (3房)
 $4296万
 $41,750/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -7892,7 +7892,7 @@
           <t>B | 1074呎 (3房)
 $4962万
 $46,199/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -7900,7 +7900,7 @@
           <t>C | 1017呎 (3房)
 $4261万
 $41,900/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr"/>
@@ -7918,7 +7918,7 @@
           <t>A | 1029呎 (3房)
 $4425万
 $43,000/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7926,7 +7926,7 @@
           <t>B | 1074呎 (3房)
 $5102万
 $47,500/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -7934,7 +7934,7 @@
           <t>C | 1017呎 (3房)
 $4231万
 $41,600/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr"/>
@@ -7952,7 +7952,7 @@
           <t>A | 635呎 (2房)
 $2559万
 $40,300/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -7960,7 +7960,7 @@
           <t>B | 511呎 (2房)
 $1993万
 $39,000/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -7968,7 +7968,7 @@
           <t>C | 512呎 (2房)
 $2381万
 $46,500/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -7976,7 +7976,7 @@
           <t>D | 635呎 (2房)
 $2413万
 $38,000/呎
-(26年-03月-22日)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -7984,7 +7984,7 @@
           <t>E | 380呎 (1房)
 $1490万
 $39,200/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -7992,7 +7992,7 @@
           <t>F | 380呎 (1房)
 $1486万
 $39,100/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
           <t>A | 635呎 (2房)
 $2426万
 $38,200/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -8015,7 +8015,7 @@
           <t>B | 511呎 (2房)
 $1955万
 $38,250/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -8023,7 +8023,7 @@
           <t>C | 512呎 (2房)
 $1930万
 $37,695/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -8031,7 +8031,7 @@
           <t>D | 635呎 (2房)
 $2350万
 $37,000/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -8039,7 +8039,7 @@
           <t>E | 380呎 (1房)
 $1467万
 $38,600/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -8047,7 +8047,7 @@
           <t>F | 380呎 (1房)
 $1459万
 $38,400/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -8062,7 +8062,7 @@
           <t>A | 635呎 (2房)
 $2264万
 $35,650/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -8070,7 +8070,7 @@
           <t>B | 511呎 (2房)
 $1864万
 $36,470/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -8078,7 +8078,7 @@
           <t>C | 512呎 (2房)
 $1847万
 $36,080/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -8086,7 +8086,7 @@
           <t>D | 635呎 (2房)
 $2197万
 $34,600/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -8094,7 +8094,7 @@
           <t>E | 380呎 (1房)
 $1368万
 $36,000/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -8102,7 +8102,7 @@
           <t>F | 380呎 (1房)
 $1376万
 $36,200/呎
-(26年-03月-23日)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -8117,7 +8117,7 @@
           <t>A | 635呎 (2房)
 $2203万
 $34,700/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -8125,7 +8125,7 @@
           <t>B | 511呎 (2房)
 $1840万
 $36,000/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -8133,7 +8133,7 @@
           <t>C | 512呎 (2房)
 $1828万
 $35,700/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -8141,7 +8141,7 @@
           <t>D | 635呎 (2房)
 $2178万
 $34,300/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -8149,7 +8149,7 @@
           <t>E | 380呎 (1房)
 $1360万
 $35,800/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -8157,7 +8157,7 @@
           <t>F | 380呎 (1房)
 $1368万
 $36,000/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
           <t>A | 635呎 (2房)
 $2165万
 $34,099/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -8180,7 +8180,7 @@
           <t>B | 511呎 (2房)
 $1809万
 $35,399/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -8188,7 +8188,7 @@
           <t>C | 512呎 (2房)
 $1792万
 $35,000/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -8196,7 +8196,7 @@
           <t>D | 635呎 (2房)
 $2134万
 $33,600/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -8204,7 +8204,7 @@
           <t>E | 380呎 (1房)
 $1315万
 $34,600/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -8212,7 +8212,7 @@
           <t>F | 380呎 (1房)
 $1319万
 $34,700/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8227,7 @@
           <t>A | 635呎 (2房)
 $2165万
 $34,100/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -8235,7 +8235,7 @@
           <t>B | 511呎 (2房)
 $1814万
 $35,500/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -8243,7 +8243,7 @@
           <t>C | 512呎 (2房)
 $1780万
 $34,766/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -8251,7 +8251,7 @@
           <t>D | 635呎 (2房)
 $2140万
 $33,700/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -8259,7 +8259,7 @@
           <t>E | 380呎 (1房)
 $1292万
 $34,000/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -8267,7 +8267,7 @@
           <t>F | 380呎 (1房)
 $1303万
 $34,300/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8282,7 @@
           <t>A | 635呎 (2房)
 $2153万
 $33,900/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -8290,7 +8290,7 @@
           <t>B | 511呎 (2房)
 $1804万
 $35,300/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -8298,7 +8298,7 @@
           <t>C | 512呎 (2房)
 $1792万
 $35,000/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -8306,7 +8306,7 @@
           <t>D | 635呎 (2房)
 $2127万
 $33,500/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -8314,7 +8314,7 @@
           <t>E | 380呎 (1房)
 $1349万
 $35,490/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -8322,7 +8322,7 @@
           <t>F | 380呎 (1房)
 $1357万
 $35,700/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -8337,7 +8337,7 @@
           <t>A | 635呎 (2房)
 $2146万
 $33,800/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -8345,7 +8345,7 @@
           <t>B | 511呎 (2房)
 $1799万
 $35,200/呎
-(26年-03月-17日)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -8353,7 +8353,7 @@
           <t>C | 512呎 (2房)
 $1782万
 $34,800/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -8361,7 +8361,7 @@
           <t>D | 635呎 (2房)
 $2121万
 $33,400/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -8369,7 +8369,7 @@
           <t>E | 380呎 (1房)
 $1264万
 $33,250/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -8377,7 +8377,7 @@
           <t>F | 380呎 (1房)
 $1281万
 $33,700/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
           <t>A | 635呎 (2房)
 $2134万
 $33,600/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -8400,7 +8400,7 @@
           <t>B | 511呎 (2房)
 $1794万
 $35,100/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -8408,7 +8408,7 @@
           <t>C | 512呎 (2房)
 $1772万
 $34,600/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -8416,7 +8416,7 @@
           <t>D | 635呎 (2房)
 $2108万
 $33,200/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -8424,7 +8424,7 @@
           <t>E | 380呎 (1房)
 $1250万
 $32,900/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -8432,7 +8432,7 @@
           <t>F | 380呎 (1房)
 $1258万
 $33,100/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
           <t>A | 1055呎 (3房)
 $4716万
 $44,700/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -8455,7 +8455,7 @@
           <t>B | 509呎 (2房)
 $1822万
 $35,800/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -8463,7 +8463,7 @@
           <t>C | 510呎 (2房)
 $1800万
 $35,300/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -8471,7 +8471,7 @@
           <t>D | 1055呎 (3房)
 $4610万
 $43,700/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr"/>

--- a/港岛-半山-雅盈峰/雅盈峰_销控明细表.xlsx
+++ b/港岛-半山-雅盈峰/雅盈峰_销控明细表.xlsx
@@ -1455,7 +1455,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -7600,7 +7600,7 @@
           <t>B | 1254呎 (3房)
 $9029万
 $72,000/呎
-(26年-07月-04日)</t>
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr"/>
